--- a/Documents/ClassicalMusic.xlsx
+++ b/Documents/ClassicalMusic.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\ClassicalMusic\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01851ECC-1FA8-4451-8BAE-FA33018B5BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBAB8D1-3B4B-4C8E-B4BA-D6EB9E3FC714}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EFEBA440-645A-481A-A4A5-DA94999A9771}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{EFEBA440-645A-481A-A4A5-DA94999A9771}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Thaat" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="138">
   <si>
     <t>Yaman</t>
   </si>
@@ -90,48 +91,18 @@
     <t>Samvadi</t>
   </si>
   <si>
-    <t>Swara</t>
-  </si>
-  <si>
     <t>ThaatID</t>
   </si>
   <si>
-    <t>MusicTypeID</t>
-  </si>
-  <si>
-    <t>AppResourceID</t>
-  </si>
-  <si>
     <t>RaagaDesc</t>
   </si>
   <si>
     <t>NyasaSwara</t>
   </si>
   <si>
-    <t>IsActive</t>
-  </si>
-  <si>
-    <t>AddedBy</t>
-  </si>
-  <si>
-    <t>AddedDate</t>
-  </si>
-  <si>
-    <t>ModifiedBy</t>
-  </si>
-  <si>
-    <t>ModifiedDate</t>
-  </si>
-  <si>
     <t>Jati</t>
   </si>
   <si>
-    <t>ThaatName</t>
-  </si>
-  <si>
-    <t>ThaatDesc</t>
-  </si>
-  <si>
     <t>Bilawal</t>
   </si>
   <si>
@@ -192,47 +163,522 @@
     <t>Komal Re, Ga, Dha and Tivra Ma – very emotional and deep.</t>
   </si>
   <si>
-    <t>Hindustani</t>
-  </si>
-  <si>
-    <t>North Indian classical music tradition</t>
-  </si>
-  <si>
-    <t>Carnatic</t>
-  </si>
-  <si>
-    <t>South Indian classical music tradition</t>
-  </si>
-  <si>
-    <t>Odissi</t>
-  </si>
-  <si>
-    <t>Odisha’s classical music tradition</t>
-  </si>
-  <si>
-    <t>Bollywood</t>
-  </si>
-  <si>
-    <t>Hindi film song</t>
-  </si>
-  <si>
-    <t>Ollywood</t>
-  </si>
-  <si>
-    <t>Odia film song</t>
-  </si>
-  <si>
-    <t>Sargam Geet</t>
-  </si>
-  <si>
-    <t>Bandish</t>
+    <t>Jog</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <r>
+      <t>Bright, joyful, natural notes (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>shuddha swaras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Serene, devotional, with brilliance (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>teevra Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Romantic, sensuous (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Folk-like, soulful (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Ga, Ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Emotional, serious (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Ga, Dha, Ni</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Austere, meditative (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Re, Dha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Devotional, pathos-filled (4 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal swaras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Intense, serious (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Re, teevra Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Mysterious, grave (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Re, Dha + teevra Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Complex, poignant (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>komal Re, Ga, Dha + teevra Ma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>P̣ ḍ Ḍ ṇ Ṇ S r R g G M Ḿ P d D n N Ṡ ṙ Ṙ  ġ Ġ ṁ Ṁ Ṗ</t>
+  </si>
+  <si>
+    <t>S R G M P D N Ṡ</t>
+  </si>
+  <si>
+    <t>S R G M  P D n Ṡ</t>
+  </si>
+  <si>
+    <t>S R g M P D n Ṡ</t>
+  </si>
+  <si>
+    <t>S R g M P d n Ṡ</t>
+  </si>
+  <si>
+    <t>S R G Ḿ P D N Ṡ</t>
+  </si>
+  <si>
+    <t>S r G M P d N Ṡ</t>
+  </si>
+  <si>
+    <t>S r g M P d n Ṡ</t>
+  </si>
+  <si>
+    <t>S r G Ḿ P D N Ṡ</t>
+  </si>
+  <si>
+    <t>S r G Ḿ P d N Ṡ</t>
+  </si>
+  <si>
+    <t>S r g Ḿ P d N Ṡ</t>
+  </si>
+  <si>
+    <t>Ṡ N d P Ḿ g r S</t>
+  </si>
+  <si>
+    <t>Ṡ N d P Ḿ G r S</t>
+  </si>
+  <si>
+    <t>Ṡ N D P Ḿ G r S</t>
+  </si>
+  <si>
+    <t>Ṡ N D P M G R S</t>
+  </si>
+  <si>
+    <t>Ṡ n D P M G R S</t>
+  </si>
+  <si>
+    <t>Ṡ N d P M G r S</t>
+  </si>
+  <si>
+    <t>Ṡ n d P M g R S</t>
+  </si>
+  <si>
+    <t>Ṡ n D P M g R S</t>
+  </si>
+  <si>
+    <t>Ṡ n d P M g r S</t>
+  </si>
+  <si>
+    <t>INSERT INTO Raaga (</t>
+  </si>
+  <si>
+    <t>Audav–Shadav</t>
+  </si>
+  <si>
+    <t>Late night (2nd prahar of night)</t>
+  </si>
+  <si>
+    <t>Thaat</t>
+  </si>
+  <si>
+    <t>Romantic, Mysterious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S G M P n Ṡ </t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>G M P, n P, M G M g S</t>
+  </si>
+  <si>
+    <t>M S n</t>
+  </si>
+  <si>
+    <t>Jog is special because it uses both shuddha and komal Ga, giving it a unique and haunting sweetness.</t>
+  </si>
+  <si>
+    <t>Bhupali</t>
+  </si>
+  <si>
+    <t>Audav–Audav</t>
+  </si>
+  <si>
+    <t>Evening (1st prahar of night, 6–9 pm)</t>
+  </si>
+  <si>
+    <t>Peaceful, Devotional</t>
+  </si>
+  <si>
+    <t>G R, G P, D P, G R S</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>G D S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S R G P D Ṡ </t>
+  </si>
+  <si>
+    <t>Ṡ D P G R S</t>
+  </si>
+  <si>
+    <t>Raag Bhupali is a serene pentatonic raga of the Kalyan thaat, evoking devotion and peace with its simple yet majestic structure.
+It omits Ma and Ni, and rests mainly on Ga, Dha, and Sa, giving it a prayerful and meditative character.</t>
+  </si>
+  <si>
+    <t>Audav–Sampurna</t>
+  </si>
+  <si>
+    <t>Bhimpalasi</t>
+  </si>
+  <si>
+    <t>Afternoon (2nd prahar, around 12–3 pm)</t>
+  </si>
+  <si>
+    <t>Romantic, Devotional, Viraha</t>
+  </si>
+  <si>
+    <t>ṇ S g M P n Ṡ</t>
+  </si>
+  <si>
+    <t>ṇ S, g M P, n Ṡ; P M g R S</t>
+  </si>
+  <si>
+    <t>Raag Bhimpalasi is a soulful afternoon raga of Kafi thaat, filled with devotion and longing.
+Its essence lies in the plaintive use of komal Ga and Ni, with repose on Ma and Sa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shivaranjani </t>
+  </si>
+  <si>
+    <t>Sad, Devotional, Romantic</t>
+  </si>
+  <si>
+    <t>R g P ; D P g R ; g S R D S ;</t>
+  </si>
+  <si>
+    <t>2nd Prahar of the Night (9PM to 12AM) or Midnight</t>
+  </si>
+  <si>
+    <t>Raag Shivranjani is a very melodious and straightforward Raag. This Raag is similar to Raag Bhoopali but has Gandhar Komal instead of Shuddha Gandhar. It can be expanded freely in all the three octaves.</t>
+  </si>
+  <si>
+    <t>P S</t>
+  </si>
+  <si>
+    <t>Ṡ n P M G M g S, S</t>
+  </si>
+  <si>
+    <t>Hansdhwani</t>
+  </si>
+  <si>
+    <t>Audhav - Audhav</t>
+  </si>
+  <si>
+    <t>Madhyam and Dhaivat Varjya. Rest all Shuddha Swaras.</t>
+  </si>
+  <si>
+    <t>G P N - S' N P G;</t>
+  </si>
+  <si>
+    <t>2nd Prahar of the Night (9PM to 12AM)</t>
+  </si>
+  <si>
+    <t>S R g P D Ṡ</t>
+  </si>
+  <si>
+    <t>Ṡ D P g R S; R, Ḍ S</t>
+  </si>
+  <si>
+    <t>S R G P N Ṡ</t>
+  </si>
+  <si>
+    <t>Ṇ RG P G R G P N Ṡ; Ṡ N P G R G P G R S;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ṡ N P G R S Ṇ, P Ṇ R S</t>
+  </si>
+  <si>
+    <t>Pilu</t>
+  </si>
+  <si>
+    <t>S; G; P; N; - n; P; g;</t>
+  </si>
+  <si>
+    <t>Audhav - Sampurna</t>
+  </si>
+  <si>
+    <t>3rd Prahar of the Day (12PM to 3PM)</t>
+  </si>
+  <si>
+    <t>Devotional, Piety</t>
+  </si>
+  <si>
+    <t>Rishabh and Dhaivat Varjya in Aaroh. Both Gandhars, Both Dhaivats, Both Nishads. Rest all Shuddha Swaras. In this Raag Komal Nishad is used with Shuddha Dhaivat and Shuddha Nishad is used with Komal Dhaivat. This Raag is expandable in Mandra and Madhya Octaves.</t>
+  </si>
+  <si>
+    <t>Gandhar and Nishad Varjya. Rest all Shuddha Swaras.</t>
+  </si>
+  <si>
+    <t>M P D ; M R ,D S ; R R P;</t>
+  </si>
+  <si>
+    <t>S G M P N Ṡ</t>
+  </si>
+  <si>
+    <t>Ṡ n D P M g R S ; ,N S g R S ;</t>
+  </si>
+  <si>
+    <t>G M P N Ṡ ; n D P ; M P N d P ; M g R S ; P g R S ,N ; S g R S ;</t>
+  </si>
+  <si>
+    <t>S R M P D Ṡ</t>
+  </si>
+  <si>
+    <t>Ṡ D P D M R S Ḍ S</t>
+  </si>
+  <si>
+    <t>M P D ; M R Ḍ S ; R R P;</t>
+  </si>
+  <si>
+    <t>Durga</t>
+  </si>
+  <si>
+    <t>Cheerful, Devotional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,13 +686,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -261,8 +754,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,416 +1082,959 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572CF824-8FDB-4681-8345-C8E65764B98D}">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultColWidth="50.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="str">
+        <f>_xlfn.CONCAT("UPDATE Thhat SET ThaatName=N'", C1,"', ThaatDesc=N'",D1,"',Aroh=N'",E1,"', Avroh=N'",F1,"' WHERE ID=",B1)</f>
+        <v>UPDATE Thhat SET ThaatName=N'Bilawal', ThaatDesc=N'Bright, joyful, natural notes (shuddha swaras)',Aroh=N'S R G M P D N Ṡ', Avroh=N'Ṡ N D P M G R S' WHERE ID=1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="str">
+        <f t="shared" ref="G2:G10" si="0">_xlfn.CONCAT("UPDATE Thhat SET ThaatName=N'", C2,"', ThaatDesc=N'",D2,"',Aroh=N'",E2,"', Avroh=N'",F2,"' WHERE ID=",B2)</f>
+        <v>UPDATE Thhat SET ThaatName=N'Kalyan', ThaatDesc=N'Serene, devotional, with brilliance (teevra Ma)',Aroh=N'S R G Ḿ P D N Ṡ', Avroh=N'Ṡ N D P Ḿ G R S' WHERE ID=2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Khamaj', ThaatDesc=N'Romantic, sensuous (komal Ni)',Aroh=N'S R G M  P D n Ṡ', Avroh=N'Ṡ n D P M G R S' WHERE ID=3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Kafi', ThaatDesc=N'Folk-like, soulful (komal Ga, Ni)',Aroh=N'S R g M P D n Ṡ', Avroh=N'Ṡ n D P M g R S' WHERE ID=4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Asavari', ThaatDesc=N'Emotional, serious (komal Ga, Dha, Ni)',Aroh=N'S R g M P d n Ṡ', Avroh=N'Ṡ n d P M g R S' WHERE ID=5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Bhairav', ThaatDesc=N'Austere, meditative (komal Re, Dha)',Aroh=N'S r G M P d N Ṡ', Avroh=N'Ṡ N d P M G r S' WHERE ID=6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Bhairavi', ThaatDesc=N'Devotional, pathos-filled (4 komal swaras)',Aroh=N'S r g M P d n Ṡ', Avroh=N'Ṡ n d P M g r S' WHERE ID=7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Marwa', ThaatDesc=N'Intense, serious (komal Re, teevra Ma)',Aroh=N'S r G Ḿ P D N Ṡ', Avroh=N'Ṡ N D P Ḿ G r S' WHERE ID=8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Poorvi', ThaatDesc=N'Mysterious, grave (komal Re, Dha + teevra Ma)',Aroh=N'S r G Ḿ P d N Ṡ', Avroh=N'Ṡ N d P Ḿ G r S' WHERE ID=9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>UPDATE Thhat SET ThaatName=N'Todi', ThaatDesc=N'Complex, poignant (komal Re, Ga, Dha + teevra Ma)',Aroh=N'S r g Ḿ P d N Ṡ', Avroh=N'Ṡ N d P Ḿ g r S' WHERE ID=10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19">
+        <f>VLOOKUP(B19,A1:B10,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" t="s">
+        <v>38</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A172A98-A47C-423B-98D0-36750CD6D3DC}">
-  <dimension ref="B1:AG19"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" customWidth="1"/>
+    <col min="14" max="14" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="15.5703125" customWidth="1"/>
+    <col min="18" max="18" width="32.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L1" t="s">
+      <c r="K1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
+      <c r="L1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="N1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="O1" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="str">
+        <f>_xlfn.CONCAT("(N'",C3,"',N'", TRIM(D3),"',N'", E3, "',N'", F3,"',N'",TRIM(G3),"',N'",TRIM(H3),"',N'", TRIM(I3), "',N'", J3, "',N'", K3, "',N'", L3, "',N'", M3,"',",N3,"),")</f>
+        <v>(N'Jog',N'Audav–Shadav',N'Late night (2nd prahar of night)',N'Romantic, Mysterious',N'S G M P n Ṡ',N'Ṡ n P M G M g S, S',N'G M P, n P, M G M g S',N'M',N'S',N'M S n',N'Jog is special because it uses both shuddha and komal Ga, giving it a unique and haunting sweetness.',4),</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>86</v>
+      </c>
+      <c r="M3" t="s">
+        <v>87</v>
+      </c>
+      <c r="N3" s="1">
+        <f>VLOOKUP(O3,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="4" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="6"/>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" t="s">
+        <v>97</v>
+      </c>
+      <c r="N4" s="1">
+        <f>VLOOKUP(O4,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="O4" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" t="s">
+    </row>
+    <row r="5" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="6"/>
+      <c r="C5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" s="1">
+        <f>VLOOKUP(O5,Thaat!$A$1:$B$10,2,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="J2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="A6" s="6"/>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M6" t="s">
+        <v>109</v>
+      </c>
+      <c r="N6" s="1">
+        <f>VLOOKUP(O6,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="A7" s="6"/>
+      <c r="C7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" t="s">
+        <v>120</v>
+      </c>
+      <c r="J7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M7" t="s">
+        <v>114</v>
+      </c>
+      <c r="N7" s="1">
+        <f>VLOOKUP(O7,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="O7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="A8" s="6"/>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J8" t="s">
         <v>6</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K8" t="s">
         <v>7</v>
       </c>
-      <c r="M2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>10</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2" t="s">
-        <v>8</v>
-      </c>
-      <c r="T2" t="s">
-        <v>8</v>
-      </c>
-      <c r="U2" t="s">
-        <v>8</v>
-      </c>
-      <c r="V2" t="s">
-        <v>8</v>
-      </c>
-      <c r="W2" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF2">
-        <v>1</v>
-      </c>
-      <c r="AG2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC3" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD3">
-        <v>2</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF3">
-        <v>1</v>
-      </c>
-      <c r="AG3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC4" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD4">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>40</v>
-      </c>
-      <c r="AF4">
-        <v>1</v>
-      </c>
-      <c r="AG4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC5" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD5">
+      <c r="L8" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" t="s">
+        <v>127</v>
+      </c>
+      <c r="N8" s="1">
+        <f>VLOOKUP(O8,Thaat!$A$1:$B$10,2,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="AE5" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF5">
-        <v>1</v>
-      </c>
-      <c r="AG5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD6">
-        <v>5</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
-      <c r="AG6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD7">
-        <v>6</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF7">
-        <v>1</v>
-      </c>
-      <c r="AG7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC8" t="s">
+      <c r="O8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="A9" s="6"/>
+      <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" t="s">
         <v>47</v>
       </c>
-      <c r="AD8">
-        <v>7</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF8">
-        <v>1</v>
-      </c>
-      <c r="AG8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC9" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD9">
-        <v>8</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF9">
-        <v>1</v>
-      </c>
-      <c r="AG9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC10" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD10">
-        <v>9</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF10">
-        <v>1</v>
-      </c>
-      <c r="AG10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AC11" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD11">
-        <v>10</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AF11">
-        <v>1</v>
-      </c>
-      <c r="AG11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>55</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AB14">
-        <v>2</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AB15">
-        <v>3</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="AB16">
-        <v>4</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="28:31" x14ac:dyDescent="0.25">
-      <c r="AB17">
-        <v>5</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="28:31" x14ac:dyDescent="0.25">
-      <c r="AB18">
-        <v>6</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="28:31" x14ac:dyDescent="0.25">
-      <c r="AB19">
-        <v>7</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
+      <c r="L9" t="s">
+        <v>129</v>
+      </c>
+      <c r="M9" t="s">
+        <v>128</v>
+      </c>
+      <c r="N9" s="1">
+        <f>VLOOKUP(O9,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N10" s="1" t="e">
+        <f>VLOOKUP(O10,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N11" s="1" t="e">
+        <f>VLOOKUP(O11,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N12" s="1" t="e">
+        <f>VLOOKUP(O12,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N13" s="1" t="e">
+        <f>VLOOKUP(O13,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N14" s="1" t="e">
+        <f>VLOOKUP(O14,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N15" s="1" t="e">
+        <f>VLOOKUP(O15,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="24" x14ac:dyDescent="0.45">
+      <c r="N16" s="1" t="e">
+        <f>VLOOKUP(O16,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="14:14" ht="24" x14ac:dyDescent="0.45">
+      <c r="N17" s="1" t="e">
+        <f>VLOOKUP(O17,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="14:14" ht="24" x14ac:dyDescent="0.45">
+      <c r="N18" s="1" t="e">
+        <f>VLOOKUP(O18,Thaat!$A$1:$B$10,2,FALSE)</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
